--- a/output/anova_test.xlsx
+++ b/output/anova_test.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6666.774275286043</v>
+        <v>7234.75159154661</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>22.30824191796508</v>
+        <v>27.77731247669149</v>
       </c>
       <c r="E2" t="n">
-        <v>2.987830159829243e-05</v>
+        <v>5.318226319293274e-06</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2903.584421383428</v>
+        <v>2775.522743677574</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.715922727663823</v>
+        <v>10.656421517966</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003423320663578338</v>
+        <v>0.002287156903596398</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.77220488847898</v>
+        <v>1.714171027464989</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1397774116267061</v>
+        <v>0.00658143733974526</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7105272842601172</v>
+        <v>0.9357566096591005</v>
       </c>
     </row>
     <row r="5">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4027.687935613409</v>
+        <v>3571.788853773241</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>13.47737798335435</v>
+        <v>13.71362842753989</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0007218141192743501</v>
+        <v>0.0006576478257091272</v>
       </c>
     </row>
     <row r="6">
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110.1706797739768</v>
+        <v>33.99944628205073</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3686511759930685</v>
+        <v>0.1305384478597029</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5472593759651527</v>
+        <v>0.7198244155709754</v>
       </c>
     </row>
     <row r="7">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14848.41781712431</v>
+        <v>15306.60635500346</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>49.68551252610391</v>
+        <v>58.76862284773356</v>
       </c>
       <c r="E7" t="n">
-        <v>1.836964274600885e-08</v>
+        <v>2.656086872573239e-09</v>
       </c>
     </row>
     <row r="8">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11655.07338912133</v>
+        <v>10157.76138555809</v>
       </c>
       <c r="C8" t="n">
         <v>39</v>
